--- a/medicao_energia_2024.xlsx
+++ b/medicao_energia_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7BDA1A-8776-426D-8E5B-12CF7E013723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76571D18-764F-4302-B567-438DCB275AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
